--- a/Django.xlsx
+++ b/Django.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Django\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAFF155-59EE-439B-990D-4BC9163D8CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43699E7E-B644-48C7-B500-58C26C66609A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0FFEE4F1-0908-4232-AD41-10A73D286687}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="7270" xr2:uid="{0FFEE4F1-0908-4232-AD41-10A73D286687}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Let's separate the whole Django into two part, backend and api</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>Condition Inside a Block</t>
+  </si>
+  <si>
+    <t>ctrl+, then emmit : key django-html value html</t>
   </si>
 </sst>
 </file>
@@ -495,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D723068F-9FA8-4FF8-81EB-8C964E855B9A}">
-  <dimension ref="B3:D32"/>
+  <dimension ref="B3:D36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="70.90625" customWidth="1"/>
@@ -632,6 +635,11 @@
         <v>25</v>
       </c>
     </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Django.xlsx
+++ b/Django.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Django\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43699E7E-B644-48C7-B500-58C26C66609A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309284D7-EDE1-4F3C-9CA3-0F33E1164702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="7270" xr2:uid="{0FFEE4F1-0908-4232-AD41-10A73D286687}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0FFEE4F1-0908-4232-AD41-10A73D286687}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
   <si>
     <t>Let's separate the whole Django into two part, backend and api</t>
   </si>
@@ -118,13 +118,136 @@
   </si>
   <si>
     <t>ctrl+, then emmit : key django-html value html</t>
+  </si>
+  <si>
+    <t>pip install djangorestframework</t>
+  </si>
+  <si>
+    <t>pip install django-cors-headers</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'rest_framework'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'corsheaders.middleware.CorsMiddleware'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CORS_ALLOW_ALL_ORIGINS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>True</t>
+    </r>
+  </si>
+  <si>
+    <t>pip install python-dotenv</t>
+  </si>
+  <si>
+    <t>pip install psycopg2-binary (posgressql)</t>
+  </si>
+  <si>
+    <t>Best workflow: Model → Serializer → View → URL.</t>
+  </si>
+  <si>
+    <t>Model → Admin (optional) → Serializer → View → URL → Client</t>
+  </si>
+  <si>
+    <t>pip install pillow (for image)</t>
+  </si>
+  <si>
+    <t>Model        → Database structure</t>
+  </si>
+  <si>
+    <t>Serializer   → Data translation + validation (Model ↔ JSON)</t>
+  </si>
+  <si>
+    <t>View         → Request handling + business workflow</t>
+  </si>
+  <si>
+    <t>URL          → Routing</t>
+  </si>
+  <si>
+    <t>Admin        → Internal management UI</t>
+  </si>
+  <si>
+    <t>serializer model data (db data ) ke json a convert kore</t>
+  </si>
+  <si>
+    <t>pip install ollama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">py -m venv venv </t>
+  </si>
+  <si>
+    <t>models.py     → database structure</t>
+  </si>
+  <si>
+    <t>serializers.py → data conversion + validation</t>
+  </si>
+  <si>
+    <t>views.py      → business logic</t>
+  </si>
+  <si>
+    <t>urls.py        → routing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For creating virtual environment - </t>
+  </si>
+  <si>
+    <t>venv\Scripts\activate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,6 +261,30 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF4FC1FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF569CD6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -178,12 +325,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D723068F-9FA8-4FF8-81EB-8C964E855B9A}">
-  <dimension ref="B3:D36"/>
+  <dimension ref="B3:E44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="70.90625" customWidth="1"/>
@@ -507,7 +663,7 @@
     <col min="6" max="6" width="70.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,7 +671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
@@ -523,7 +679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
@@ -531,22 +687,25 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
@@ -554,12 +713,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
@@ -567,77 +726,173 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="D26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="D32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D34" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Django.xlsx
+++ b/Django.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Django\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309284D7-EDE1-4F3C-9CA3-0F33E1164702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8498F0FF-D04C-4621-94EB-CE0A7202299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0FFEE4F1-0908-4232-AD41-10A73D286687}"/>
   </bookViews>

--- a/Django.xlsx
+++ b/Django.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Django\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8498F0FF-D04C-4621-94EB-CE0A7202299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AFEA7D-8474-4B57-87E1-5A580D0A72A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0FFEE4F1-0908-4232-AD41-10A73D286687}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
   <si>
     <t>Let's separate the whole Django into two part, backend and api</t>
   </si>
@@ -241,6 +241,66 @@
   </si>
   <si>
     <t>venv\Scripts\activate</t>
+  </si>
+  <si>
+    <t>import uuid</t>
+  </si>
+  <si>
+    <t>class Product(models.Model):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    id = models.UUIDField(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        primary_key=True,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        default=uuid.uuid4,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        editable=False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This will create a uuid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        raise PermissionDenied("You do not have permission.")</t>
+  </si>
+  <si>
+    <t>from rest_framework import viewsets</t>
+  </si>
+  <si>
+    <t>from rest_framework.permissions import IsAuthenticated, AllowAny</t>
+  </si>
+  <si>
+    <t>from rest_framework.exceptions import PermissionDenied</t>
+  </si>
+  <si>
+    <t>class PostViewSet(viewsets.ModelViewSet):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    queryset = Post.objects.all()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    serializer_class = PostSerializer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    def get_permissions(self):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        # Allow only list page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if self.action == "list":</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            return [IsAuthenticated()]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        # Block details/update/delete/create</t>
   </si>
 </sst>
 </file>
@@ -654,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D723068F-9FA8-4FF8-81EB-8C964E855B9A}">
-  <dimension ref="B3:E44"/>
+  <dimension ref="B3:E83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="70.90625" customWidth="1"/>
@@ -895,6 +955,106 @@
         <v>42</v>
       </c>
     </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Django.xlsx
+++ b/Django.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Django\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AFEA7D-8474-4B57-87E1-5A580D0A72A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6E2D39-5B06-4EB9-BCBD-BC3D0CBE8BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0FFEE4F1-0908-4232-AD41-10A73D286687}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
   <si>
     <t>Let's separate the whole Django into two part, backend and api</t>
   </si>
@@ -302,12 +302,18 @@
   <si>
     <t xml:space="preserve">        # Block details/update/delete/create</t>
   </si>
+  <si>
+    <t xml:space="preserve"> , backend folder , venv create,django-admin startproject core-backend . djnago install</t>
+  </si>
+  <si>
+    <t>Starter</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,6 +351,14 @@
       <color rgb="FF569CD6"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -385,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -399,6 +413,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -719,7 +736,7 @@
   <cols>
     <col min="2" max="2" width="70.90625" customWidth="1"/>
     <col min="4" max="4" width="62.7265625" customWidth="1"/>
-    <col min="5" max="5" width="58.7265625" customWidth="1"/>
+    <col min="5" max="5" width="78.90625" customWidth="1"/>
     <col min="6" max="6" width="70.90625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -759,10 +776,16 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
+      <c r="E7" s="8" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.35">

--- a/Django.xlsx
+++ b/Django.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Django\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6E2D39-5B06-4EB9-BCBD-BC3D0CBE8BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8265596-1917-48BF-BF20-59042F3DCE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0FFEE4F1-0908-4232-AD41-10A73D286687}"/>
   </bookViews>

--- a/Django.xlsx
+++ b/Django.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Django\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8265596-1917-48BF-BF20-59042F3DCE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E691551A-8A98-4AF0-92F3-8EEC8A8DA767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0FFEE4F1-0908-4232-AD41-10A73D286687}"/>
   </bookViews>
